--- a/data/source/pops_list_full.xlsx
+++ b/data/source/pops_list_full.xlsx
@@ -116,11 +116,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="144.09765625" customWidth="true"/>
-    <col min="2" max="2" width="37.08984375" customWidth="true"/>
+    <col min="2" max="2" width="63.08984375" customWidth="true"/>
     <col min="3" max="3" width="15.5078125" customWidth="true"/>
     <col min="4" max="4" width="16.8984375" customWidth="true"/>
     <col min="5" max="5" width="21.3359375" customWidth="true"/>
@@ -174,27 +174,27 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2-(2H-benzotriazol-2-yl)-4,6-di-tert-pentylphenol</t>
+          <t>1,6,7,8,9,14,15,16,17,17,18,18-Dodecachloropentacyclo[12.2.1.16,9.02,13.05,10]octadeca-7,15-diene (“Dechlorane Plus”™)</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>covering any of its individual anti- and syn-isomers or any combination thereof</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>247-384-8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>25973-55-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>15-Jul-2025</t>
+          <t>25-Sep-2025</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -209,14 +209,14 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>15-Jul-2025</t>
+          <t>25-Sep-2025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>Methoxychlor</t>
+          <t>2-(2H-benzotriazol-2-yl)-4,6-di-tert-pentylphenol</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -226,17 +226,17 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>200-779-9</t>
+          <t>247-384-8</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>72-43-5</t>
+          <t>25973-55-1</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>27-Sep-2024</t>
+          <t>15-Jul-2025</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -251,14 +251,14 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>27-Sep-2024</t>
+          <t>15-Jul-2025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Perfluorohexane sulfonic acid (PFHxS), its salts and PFHxS-related compounds</t>
+          <t>Methoxychlor</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -268,23 +268,22 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200-779-9</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>72-43-5</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>29-Dec-2022</t>
+          <t>27-Sep-2024</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Annex I, part A
-Annex IV</t>
+          <t>Annex I, part A</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -294,14 +293,14 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>29-Dec-2022</t>
+          <t>27-Sep-2024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Dicofol</t>
+          <t>Perfluorohexane sulfonic acid (PFHxS), its salts and PFHxS-related compounds</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -311,17 +310,17 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>204-082-0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>115-32-2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>18-Aug-2020</t>
+          <t>29-Dec-2022</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -337,14 +336,14 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>18-Aug-2020</t>
+          <t>29-Dec-2022</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>perfluorooctanoic acid (PFOA), its salts and PFOA-related substances</t>
+          <t>Dicofol</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -354,17 +353,17 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>204-082-0</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>115-32-2</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>15-Jun-2020</t>
+          <t>18-Aug-2020</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -380,14 +379,14 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>15-Jun-2020</t>
+          <t>18-Aug-2020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Pentachlorophenol and its salts and esters</t>
+          <t>perfluorooctanoic acid (PFOA), its salts and PFOA-related substances</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -407,7 +406,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>20-Jun-2019</t>
+          <t>15-Jun-2020</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -423,14 +422,14 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>20-Jun-2019</t>
+          <t>15-Jun-2020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Bis(pentabromophenyl) ether</t>
+          <t>Pentachlorophenol and its salts and esters</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -440,12 +439,12 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>214-604-9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>1163-19-5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -473,27 +472,27 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Hexabromocyclododecane (HBCDD)</t>
+          <t>Bis(pentabromophenyl) ether</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>and all major diastereoisomers identified</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>214-604-9</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1163-19-5</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>01-Mar-2016</t>
+          <t>20-Jun-2019</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -509,40 +508,39 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>01-Mar-2016</t>
+          <t>20-Jun-2019</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Hexachlorobuta-1,3-diene</t>
+          <t>Hexabromocyclododecane (HBCDD)</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>and all major diastereoisomers identified</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>201-765-5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>87-68-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>19-Jun-2012</t>
+          <t>01-Mar-2016</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Annex I, part A
-Annex III, part B
 Annex IV</t>
         </is>
       </c>
@@ -553,14 +551,14 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>19-Jun-2012</t>
+          <t>01-Mar-2016</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Polychlorinated naphthalenes</t>
+          <t>Hexachlorobuta-1,3-diene</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -570,12 +568,12 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>201-765-5</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87-68-3</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -604,7 +602,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Endosulfan and its isomers</t>
+          <t>Polychlorinated naphthalenes</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -630,6 +628,7 @@
       <c r="F12" s="9" t="inlineStr">
         <is>
           <t>Annex I, part A
+Annex III, part B
 Annex IV</t>
         </is>
       </c>
@@ -647,7 +646,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Alkanes, C10-13, chloro</t>
+          <t>Endosulfan and its isomers</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -657,12 +656,12 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>287-476-5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>85535-84-8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -690,7 +689,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Perfluorooctane sulfonic acid (PFOS), its salts and PFOS-related compoundsC8F17SO2X (X = OH, Metal salt (O-M+ ), halide, amide, and other related compounds including polymers)</t>
+          <t>Alkanes, C10-13, chloro</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -700,17 +699,17 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>287-476-5</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85535-84-8</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>24-Aug-2010</t>
+          <t>19-Jun-2012</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -726,14 +725,14 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>24-Aug-2010</t>
+          <t>19-Jun-2012</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Pentabromodiphenyl ether (group)</t>
+          <t>Perfluorooctane sulfonic acid (PFOS), its salts and PFOS-related compoundsC8F17SO2X (X = OH, Metal salt (O-M+ ), halide, amide, and other related compounds including polymers)</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -776,7 +775,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Heptabromodiphenyl ether (Group)</t>
+          <t>Pentabromodiphenyl ether (group)</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -819,7 +818,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Tetrabromodiphenyl ether (group)</t>
+          <t>Heptabromodiphenyl ether (Group)</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -829,12 +828,12 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>254-787-2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>40088-47-9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -862,7 +861,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Hexabromodiphenyl ether (group)</t>
+          <t>Tetrabromodiphenyl ether (group)</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -872,12 +871,12 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>254-787-2</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>40088-47-9</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -905,7 +904,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Pentachlorobenzene</t>
+          <t>Hexabromodiphenyl ether (group)</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -915,12 +914,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>210-172-0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>608-93-5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -931,7 +930,6 @@
       <c r="F19" s="9" t="inlineStr">
         <is>
           <t>Annex I, part A
-Annex III, part B
 Annex IV</t>
         </is>
       </c>
@@ -949,7 +947,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Hexabromo-1,1'-biphenyl</t>
+          <t>Pentachlorobenzene</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -959,22 +957,23 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>252-994-2</t>
+          <t>210-172-0</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>36355-01-8</t>
+          <t>608-93-5</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>29-Apr-2004</t>
+          <t>24-Aug-2010</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
           <t>Annex I, part A
+Annex III, part B
 Annex IV</t>
         </is>
       </c>
@@ -985,14 +984,14 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>29-Apr-2004</t>
+          <t>24-Aug-2010</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Chlordecone</t>
+          <t>Hexabromo-1,1'-biphenyl</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1002,12 +1001,12 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>205-601-3</t>
+          <t>252-994-2</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>143-50-0</t>
+          <t>36355-01-8</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1035,7 +1034,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Chlordane , pur</t>
+          <t>Chlordecone</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1045,12 +1044,12 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>200-349-0</t>
+          <t>205-601-3</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>57-74-9</t>
+          <t>143-50-0</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1078,7 +1077,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Polychlorinated Biphenyls (PCB)</t>
+          <t>Chlordane , pur</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1088,12 +1087,12 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200-349-0</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>57-74-9</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1104,7 +1103,6 @@
       <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Annex I, part A
-Annex III, part A
 Annex IV</t>
         </is>
       </c>
@@ -1122,7 +1120,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Dieldrin</t>
+          <t>Polychlorinated Biphenyls (PCB)</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1132,12 +1130,12 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>200-484-5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>60-57-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1148,6 +1146,7 @@
       <c r="F24" s="9" t="inlineStr">
         <is>
           <t>Annex I, part A
+Annex III, part A
 Annex IV</t>
         </is>
       </c>
@@ -1165,7 +1164,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Polychlorinated dibenzo-p-dioxins and dibenzofurans (PCDD/PCDF)</t>
+          <t>Dieldrin</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1175,12 +1174,12 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>200-484-5</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60-57-1</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1190,7 +1189,7 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Annex III, part A
+          <t>Annex I, part A
 Annex IV</t>
         </is>
       </c>
@@ -1208,7 +1207,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Endrin</t>
+          <t>Polychlorinated dibenzo-p-dioxins and dibenzofurans (PCDD/PCDF)</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1218,12 +1217,12 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>200-775-7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>72-20-8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1233,7 +1232,7 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Annex I, part A
+          <t>Annex III, part A
 Annex IV</t>
         </is>
       </c>
@@ -1251,7 +1250,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Hexachlorobenzene</t>
+          <t>Endrin</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1261,12 +1260,12 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>204-273-9</t>
+          <t>200-775-7</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>118-74-1</t>
+          <t>72-20-8</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1277,7 +1276,6 @@
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Annex I, part A
-Annex III, part B
 Annex IV</t>
         </is>
       </c>
@@ -1295,7 +1293,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Hexachlorocyclohexanes, including lindane</t>
+          <t>Hexachlorobenzene</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1305,12 +1303,12 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>204-273-9</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>118-74-1</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1321,6 +1319,7 @@
       <c r="F28" s="9" t="inlineStr">
         <is>
           <t>Annex I, part A
+Annex III, part B
 Annex IV</t>
         </is>
       </c>
@@ -1338,7 +1337,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Polycyclic aromatic hydrocarbons (PAHs)</t>
+          <t>Hexachlorocyclohexanes, including lindane</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1363,7 +1362,8 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Annex III, part B</t>
+          <t>Annex I, part A
+Annex IV</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Heptachlor</t>
+          <t>Polycyclic aromatic hydrocarbons (PAHs)</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>200-962-3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>76-44-8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1405,8 +1405,7 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>Annex I, part A
-Annex IV</t>
+          <t>Annex III, part B</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -1423,7 +1422,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Dodecachloropentacyclo[5.2.1.02,6.03,9.05,8]decane</t>
+          <t>Heptachlor</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1433,12 +1432,12 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>219-196-6</t>
+          <t>200-962-3</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2385-85-5</t>
+          <t>76-44-8</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1466,7 +1465,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Clofenotane</t>
+          <t>Dodecachloropentacyclo[5.2.1.02,6.03,9.05,8]decane</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1476,12 +1475,12 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>200-024-3</t>
+          <t>219-196-6</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>50-29-3</t>
+          <t>2385-85-5</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -1509,7 +1508,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Aldrin</t>
+          <t>Clofenotane</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1519,12 +1518,12 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>206-215-8</t>
+          <t>200-024-3</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>309-00-2</t>
+          <t>50-29-3</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -1552,41 +1551,84 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>206-215-8</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>309-00-2</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>29-Apr-2004</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Annex I, part A
+Annex IV</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Inclusion in  the EU POPs Regulation</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>29-Apr-2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
           <t>Toxaphene</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>232-283-3</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>8001-35-2</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>29-Apr-2004</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Annex I, part A
-Annex IV</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>Inclusion in  the EU POPs Regulation</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>29-Apr-2004</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Annex I, part A
+Annex IV</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Inclusion in  the EU POPs Regulation</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>29-Apr-2004</t>
         </is>
